--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:48</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="22">
@@ -1021,19 +1021,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.59</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.59</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:38</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2023_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 20:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
